--- a/artfynd/A 45911-2024 artfynd.xlsx
+++ b/artfynd/A 45911-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>88237970</v>
       </c>
       <c r="B2" t="n">
-        <v>84764</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432002.2285237082</v>
+        <v>432002</v>
       </c>
       <c r="R2" t="n">
-        <v>6196868.176451434</v>
+        <v>6196868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,12 +792,7 @@
         <v>88237966</v>
       </c>
       <c r="B3" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,7 +814,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432002.2285237082</v>
+        <v>432002</v>
       </c>
       <c r="R3" t="n">
-        <v>6196868.176451434</v>
+        <v>6196868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +868,9 @@
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
